--- a/программа.xlsx
+++ b/программа.xlsx
@@ -1677,7 +1677,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>37.5x6</t>
+          <t>35x9</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,6 @@
     <row r="14" ht="18" customHeight="1"/>
     <row r="15" ht="18" customHeight="1"/>
     <row r="16" ht="18" customHeight="1"/>
-    <row r="17"/>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
         <is>
@@ -1912,7 +1911,6 @@
     <row r="27" ht="18" customHeight="1"/>
     <row r="28" ht="18" customHeight="1"/>
     <row r="29" ht="18" customHeight="1"/>
-    <row r="30"/>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="21" t="inlineStr">
         <is>
@@ -2089,7 +2087,6 @@
     <row r="40" ht="18" customHeight="1"/>
     <row r="41" ht="18" customHeight="1"/>
     <row r="42" ht="18" customHeight="1"/>
-    <row r="43"/>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="21" t="inlineStr">
         <is>
@@ -2266,7 +2263,6 @@
     <row r="53" ht="18" customHeight="1"/>
     <row r="54" ht="18" customHeight="1"/>
     <row r="55" ht="18" customHeight="1"/>
-    <row r="56"/>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="21" t="inlineStr">
         <is>
@@ -2443,7 +2439,6 @@
     <row r="66" ht="18" customHeight="1"/>
     <row r="67" ht="18" customHeight="1"/>
     <row r="68" ht="18" customHeight="1"/>
-    <row r="69"/>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="21" t="inlineStr">
         <is>
@@ -2946,7 +2941,6 @@
     <row r="105" ht="18" customHeight="1"/>
     <row r="106" ht="18" customHeight="1"/>
     <row r="107" ht="18" customHeight="1"/>
-    <row r="108"/>
     <row r="109" ht="20" customHeight="1"/>
     <row r="110" ht="22" customHeight="1"/>
     <row r="111" ht="18" customHeight="1"/>
@@ -3025,7 +3019,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="21" t="inlineStr">
         <is>
@@ -3202,7 +3195,6 @@
     <row r="14" ht="18" customHeight="1"/>
     <row r="15" ht="18" customHeight="1"/>
     <row r="16" ht="18" customHeight="1"/>
-    <row r="17"/>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
         <is>
@@ -3379,7 +3371,6 @@
     <row r="27" ht="18" customHeight="1"/>
     <row r="28" ht="18" customHeight="1"/>
     <row r="29" ht="18" customHeight="1"/>
-    <row r="30"/>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="21" t="inlineStr">
         <is>
@@ -3550,7 +3541,6 @@
     <row r="40" ht="18" customHeight="1"/>
     <row r="41" ht="18" customHeight="1"/>
     <row r="42" ht="18" customHeight="1"/>
-    <row r="43"/>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="21" t="inlineStr">
         <is>
@@ -3709,7 +3699,6 @@
     <row r="53" ht="18" customHeight="1"/>
     <row r="54" ht="18" customHeight="1"/>
     <row r="55" ht="18" customHeight="1"/>
-    <row r="56"/>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="21" t="inlineStr">
         <is>
@@ -3886,7 +3875,6 @@
     <row r="66" ht="18" customHeight="1"/>
     <row r="67" ht="18" customHeight="1"/>
     <row r="68" ht="18" customHeight="1"/>
-    <row r="69"/>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="21" t="inlineStr">
         <is>
@@ -4063,7 +4051,6 @@
     <row r="79" ht="18" customHeight="1"/>
     <row r="80" ht="18" customHeight="1"/>
     <row r="81" ht="18" customHeight="1"/>
-    <row r="82"/>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="21" t="inlineStr">
         <is>
@@ -4234,7 +4221,6 @@
     <row r="92" ht="18" customHeight="1"/>
     <row r="93" ht="18" customHeight="1"/>
     <row r="94" ht="18" customHeight="1"/>
-    <row r="95"/>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="21" t="inlineStr">
         <is>
